--- a/data/posted_pins.xlsx
+++ b/data/posted_pins.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Picture</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Affiliate Link</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3043,6 +3031,1582 @@
         </is>
       </c>
       <c r="F89" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MILTON Cryo Fridge Storage Containers for Door - Set of 6, Stackable, Space-Saving Transparent Plastic Containers with Waterproof Stickers, Multipurpose Kitchen Organizer for Fruits, Vegetables &amp; More</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/712CZ7ijrHL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B01niHzEh</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION – Celebrating 5 decades of trust, quality, and everyday solutions from Milton for kitchen accessories items for home. | KITCHEN ESSENTIALS TO MAXIMIZE FRIDGE DOOR SPACE : Designed to fit perfectly in the refrigerator side door, these kitchen organizer containers maximize space and keep your fridge neat. Ideal for storing vegetables separately to preserve freshness and reduce spoilage. Convenient, space-saving, and easy to access. | OPTIMIZE FRIDGE SHELF SPACE : Plastic container designed to make better use of horizontal fridge space—keeps items organized and easy to access without wasting shelf area. | MULTIPURPOSE STORAGE USE : Perfect for kitchen counters, drawers, or shelves—store spices, makeup, stationery, or small essentials with ease and keep your space tidy. | READY-TO-USE ORGANIZATION : Waterproof vinyl stickers help you identify contents at a glance—no more guessing, just grab and go! | SAFE &amp; DURABLE MATERIAL : Made from BPA-free, food-safe plastic, these storage boxes guarantee durability and strength. Their transparent bodies offer clear visibility of the contents stored inside, enhancing their functionality as top-notch kitchen organizer tools. lightweight yet sturdy for everyday use in any kitchen.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Clazkit Precision Cashews &amp; Almond Cutter/Slicer : Effortless Slicing with Built-in Storage Convenience -Multicolor</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81H9fjRJRFL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0aGkR0Mk</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Unparalleled Quality:** Experience unmatched quality with Clazkit's Multi Chopper and Slicer. Chop, dice, slice, or grate with ease, reducing your prep time to just a few minutes. Crafted with premium materials including steel blades and food-grade BPA-free components, this kitchen gadget ensures durability and safety. | Safety First:** The unique design of this kitchen tool prioritizes safety by keeping your hands away from the built-in blades. Enjoy expert slicing without the risk, making it the safest choice for your kitchen. | Innovative Space-Saving Design:** Free up valuable countertop space with Clazkit's innovative kitchen gadget. The Dry Fruits Slicer comes with a container to store dry fruits, preventing slippage during slicing. This design ensures a clean, safe, and efficient slicing experience, eliminating the hassles of washing and wiping. | Rust Resistant Blades:** The heavy-duty stainless steel blades maintain razor sharpness, ensuring crisp and smooth slicing and cutting. Blades are easily interchangeable for added convenience. | Easy to Clean:** Cleaning is a breeze with the EASY DISASSEMBLY design. Detachable parts allow for thorough washing, and the dry fruit cutter is also DISHWASHER SAFE, making post-cooking cleanup quick and hassle-free. Enjoy the efficiency of a top-notch kitchen tool without the added stress of cleaning up.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Solitude 4 Pcs Oval Silicone Kulfi &amp; Ice Candy Moulds with Sticks | Popsicle &amp; Ice Cream Maker Mold for Kids | Reusable BPA-Free DIY Popsicle Molds for Juice, Yogurt &amp; Fruit Treats</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51+9IPq2lmL._SY300_SX300_QL70_FMwebp_.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B02pSEjfR</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>𝐕𝐞𝐫𝐬𝐚𝐭𝐢𝐥𝐞 𝐏𝐨𝐩𝐬𝐢𝐜𝐥𝐞 𝐒𝐞𝐭: Pack of 4 reusable ice candy moulds in attractive colours, perfect for making healthy homemade popsicles, kulfi, yoghurt sticks, and frozen treats for kids &amp; adults. | 𝐅𝐨𝐨𝐝-𝐆𝐫𝐚𝐝𝐞 𝐒𝐚𝐟𝐞 𝐌𝐚𝐭𝐞𝐫𝐢𝐚𝐥: Made from high-quality BPA-free silicone that is non-toxic, durable, and flexible, ensuring safe usage and long-lasting performance. | 𝐄𝐚𝐬𝐲 𝐑𝐞𝐥𝐞𝐚𝐬𝐞 𝐃𝐞𝐬𝐢𝐠𝐧: Soft silicone body allows effortless removal of popsicles without breaking or sticking, giving you perfectly shaped ice lollies every time. | 𝐈𝐝𝐞𝐚𝐥 𝐒𝐢𝐳𝐞 &amp; 𝐂𝐚𝐩𝐚𝐜𝐢𝐭𝐲: Each mould is designed in a convenient size (approx. 9.5 cm x 5.5 cm), perfect for standard popsicles, portion control, and easy handling for kids. | 𝐄𝐚𝐬𝐲 𝐭𝐨 𝐂𝐥𝐞𝐚𝐧 &amp; 𝐑𝐞𝐮𝐬𝐞: Smooth, non-stick surface makes cleaning quick and hassle-free; it's dishwasher safe and reusable, making it eco-friendly and convenient for daily use.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>HomeWiz Large Steel Chopping Board for Kitchen - 100% Stainless Steel Cutting Board | Heavy Duty Chopping Board | Non-Porous Hygienic Surface for Vegetables, Meat &amp; Fish, Rust-Resistant | 41 x 31 cm</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/81Wry2I7hrL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0g3fFRBL</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>YOUR PLASTIC CHOPPING BOARD IS FEEDING YOUR FAMILY MICROPLASTICS — AND YOU CAN'T SEE IT HAPPENING: Every knife stroke on a plastic board shaves off fragments so small they're invisible to the naked eye. They enter your dal your sabzi your marinades. Peer-reviewed science now finds microplastics in human blood lungs and placentas. You cannot cook them out filter them out or reverse their accumulation. The only way to stop feeding your family plastic is to stop chopping on it. Permanently. | NON-POROUS STEEL THAT BACTERIA PHYSICALLY CANNOT COLONISE: Used plastic boards tested by food scientists contain bacterial colonies in their grooves at levels that would fail commercial kitchen inspections — invisible to you present in every meal. This stainless steel surface has zero pores zero grooves zero depth for anything to hide in. When you wash it you clean it. Completely. Not just on the surface. | LARGE ENOUGH — FINALLY ENOUGH BOARD TO COOK LIKE YOU ACTUALLY COOK: Small boards are the silent compromise most kitchens accept. Vegetables fall off you chop in batches you're constantly repositioning. At and this board gives you the full working surface an Indian kitchen actually demands — from daily sabzi prep to full chicken breakdown to large-batch roti rolling. | SOLID PLANTED STEEL — STAYS WHERE YOU PUT IT THROUGH THE HARDEST PREP: The weight is engineering not excess. Heavy enough to resist movement during forceful chopping and vigorous mincing. Light enough to pick up with one hand. Lay a damp cloth underneath and it becomes an immovable prep station that never requires readjusting. | DISHWASHER SAFE RUST-RESISTANT AND ZERO MAINTENANCE: The dishwasher does what it claims — fully sanitises. The rust-resistant surface handles daily moisture without corroding. No oiling no conditioning no hand-drying required (though recommended for best longevity). The board that asks nothing of you and delivers everything. | CHOPPING BOARD ROTI ROLLER SERVING PLATTER AND TRIVET IN ONE: Your steel board does not retire after prep. Slide it to the table as a rustic platter for snacks and kebabs. Roll roti and puri dough on its smooth surface. Park a hot kadai on it as a trivet. One board. Four daily functions. None of them involving microplastics. | WHY 10 LAKH INDIAN FAMILIES COOK WITH HOMEWIZ: HomeWiz was not built in a boardroom. It was built around the reality of Indian kitchens — the morning chai the Sunday biryani the daily dal that feeds a family. We started with one belief: that the tools in your kitchen should be as honest as the food you cook with them. Today over 10 lakh families across India trust HomeWiz in their homes. Not because of flashy marketing — but because when a HomeWiz product lands in your kitchen it simply works. Every single day. That is the only promise we make — and the only one we need to.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ganesh Stainless Steel Gas Lighter with Knife &amp; Peeler for Kitchen Use Restaurants Metal Gas Stove Lighter Regular Size Easy Grip, 3-Piece, Colour May Vary Colour</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51m1UiEBfdL._SY606_.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0aNxgGAt</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Premium Stainless Steel Body | Single Spark Piezo Gas Lighter | Handy &amp; Stylish Peeling Knife | Use with easy &amp; comfort | Best operational Result guaranteed</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RITU Stainless Steel Kitchen Knife and Peeler Set of 3 Combo | for Daily Use | Sharp Blades Multipurpose Peeling Cutting Tool | Rust -Resistant Durable Blades | Green Ergonomic Handle</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61e0b6+uG9L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0aewzcMC</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Premium Stainless Steel Blades - Made with high-quality stainless steel, the blades of this knife and peeler set are extremely sharp, rust resistant, and long lasting. Perfect for cutting, slicing, and peeling vegetables or fruits with precision, they retain sharpness even after regular use. A must have combo for smooth and effortless kitchen prep every day. | Ergonomic Non Slip Handle Design - Designed with user comfort in mind, each tool features a strong grip handle that fits comfortably in the hand. The green soft grip handle is non slip and easy to hold, ensuring safe usage while chopping or peeling. Ideal for prolonged usage in home kitchens without causing hand fatigue. | Multipurpose Kitchen Tool Set Of This 3 - Piece combo includes a knife and peeler set that handles a variety of kitchen tasks cutting vegetables, peeling fruits, slicing herbs, and more. Whether you're preparing salads, snacks, or full meals, this set simplifies your cooking with versatile performance and ease. | Compact, Lightweight &amp; Easy To Clean - These tools are not only easy to use but also easy to maintain. The compact and lightweight design makes them convenient to store in any kitchen drawer. The stainless steel build ensures they clean effortlessly with water and do not retain food stains or odors after washing. | Ideal For Home &amp; Travel Use - Whether you're cooking at home, in a hostel, or during travel, this knife and peeler combo is a dependable companion. Its durable build and compact size make it perfect for everyday use as well as on the go cooking. A perfect kitchen essential for both beginners and experienced cooks.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Stainless Steel Potato Vegetable Pav Bhaji Masher, Multicolour</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51nXwaaem6L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0h1f1LEz</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Easy to clean | Attractive and handy look | Elegant and must add to your dining, kitchen, cutlery list | Color: Multicolour, Material: Stainless Steel | Package Contents: 1-Piece Masher | Country of Origin: India</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kitchen Stainless Steel Garlic Press with Ergonomic Handle,Garlic Crusher, Handy Garlic Crusher, Kitchen Garlic Crushing Tool Stainless Steel (Multicolor)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51QPKhJwB+L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0a3CbyCL</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PREMIUM MATERIAL: Constructed from high-quality stainless steel for superior durability and corrosion resistance | ERGONOMIC DESIGN: Features a comfortable handle grip that reduces hand fatigue during repeated use | EFFICIENT CRUSHING: Heavy-duty pressing mechanism thoroughly minces garlic cloves with minimal effort | EASY CLEANING: Dishwasher-safe design with smooth surfaces that prevent food particles from sticking | VERSATILE USE: Suitable for crushing both peeled and unpeeled garlic cloves, perfect for daily kitchen tasks</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Stainless Steel Whisks, Hand Push Whisk Blender Semi-Automatic Whisk Mixer Egg Milk Beater Milk Frother Rotating Push Whisk Mixer for Blending, Whisking, Beating &amp; Stirring (Egg Whisker)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51n8cj-+8aL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B00QENtor</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Durable: Made of food grade stainless steel for durability and no need to worry about bending or breaking often. | Wide range of applications: Suitable for mixing, whipping and foaming of coffee drinks, or more like milkshakes, whipped cream, salad dressings, gravy, sauces, mayonnaise, meringues and even meat. | Energy saving and environmental protection: Semi-automatic design, quick and easy to use, mechanical mixing, fast mixing and mixing, saving you time. | Easy to use &amp; clean: The kitchen blender only needs to press down vertically and stir quickly to prevent excessive fatigue. Just wash with soapy water and rinse off. | Package Includes: 1 x Manual Steel Whisk, Size: 10 Inch</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>4-Slot Kitchen Cooking Utensil Stand-Multifunction Kitchen Cooking Utensil Plastic Stand Holder Pot Clips Support Spoon Stove Organizer Tool Pan Cover Lid Rack (1Pc's)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41JUmH0gS8L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0dRUAXmd</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>☯ Spoons Holder: A smart and innovative kitchen tool that will help you realize future cooking and cooking utensils stand. The perfect kitchen assistant can ensure no messy cooking. It is safe to wash and clean and easy to clean. Keeps your countertops clean and your utensils close at hand while cooking or baking. | ☯ Safe material: This utensil rest is made of safe PP material, which is non-toxic, odorless, rustproof, and waterproof. It is heat resistant and can be placed near the stove. It can also hold other kitchen tools, such as pot lids, spring clips, knives, etc. | ☯ Keeps Your Counterpart Organized: An essential cooking tool for any home chef. Our spoon rest has simple lines and a beautiful design that will keep your countertops splatter-free tools. This BPA-free utensil rest holds up to 4 spoons or spatulas and the base is designed to contain any drips. | ☯ Easy cleanup: The rack is made of non-slip silicone, which helps you keep organized kitchen utensils and keep them clean during cooking. Dishwasher safe or you just rinse with clear water. | ☯ Widely used: Widely used for kitchen utensils, gadget, table cutlery, spoon, brush, and so on, keeping your kitchen tidy and organized. You can use kitchen utensil rest to prevent messy oil, sauces, or liquids from dripping from cooking utensils, and prevent tableware from touching the table, will capture liquids and solids, easy to keep the kitchen tidy and clean.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Niwlix Microfiber Cleaning Cloth Roll Kitchen Towel Roll Reusable Kitchen Towel Micro Fiber Cloth for Car Cleaning Clothes Kitchen Cloth for Cleaning | 20 Pack</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71R1R4eYuzL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B03mzC6gw</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>🏝️【Cleaning Cloths Within Easy Reach】Keep premium microfiber cleaning cloths at your fingertips for quick and efficient cleaning. Tear off lint-free rags effortlessly to tackle kitchen messes, from stovetops, sink to glassware ceramic dishes, 20 pc replaceable wipes easily meet your daily cleaning needs. | 🏝️【Gentle and Absorbent Microfiber Towel】Kitchen cleaning cloth is made of high-quality polyester and polyamide, soft and more absorbent, will not leave scratches on the surface of items, is reusable and machine washable, and can wipe away grease from dishes without cleaning solutions. | 🏝️【Lint-Free Cleaning Rags】Enjoy the ease of lint-free cleaning with our reusable microfiber rags. These cloths effortlessly absorb water and resist lint, making them perfect for wiping away grease, dust, and water stains from various surfaces, including glass windows, stainless steel pots, ceramic tableware, kitchen tools, and car steering wheels. | 🏝️【Skin-Friendly Towel for Efficient Cleaning】Microfiber towels are soft in texture, suitable in size and easy to grab. They can better help housewives clean the kitchen and bedroom, remove stains faster and reduce labor time. | 🏝️【Versatile and Practical Rags】Microfiber towels are great for cleaning dust, dirt, oil, stains, suitable for kitchens, bathrooms, living rooms, offices, clubs, restaurants, hotels, shops. Bringing you a lot of convenience and keeping your room clean and tidy.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>hago Refrigerator Organizer Container with 6 Grid Compartments | 1200 ML Fridge Storage Box for Vegetables &amp; Fruits | BPA-Free Kitchen Storage Container for Fridge Organisation</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71QED8-OFhL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0iypKB7T</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>6 Grid Multi-Section Design Comes with 6 separate grid compartments to store different vegetables, fruits, herbs and chopped items without mixing. Perfect refrigerator organizer for daily kitchen use. | Freshness Lock ventilated body maintain ideal humidity, keeping food fresh for longer. Ideal fridge storage box for vegetables and fruits. | 1200 ML Large Capacity Spacious 1200 ML capacity suitable for storing pre-cut onions, chillies, garlic, ginger, coriander and more. Fits perfectly in all refrigerator shelves. | BPA-Free &amp; Food-Grade Plastic Made from high-quality BPA-free material, safe for food storage, odor-free, durable and easy to wash. Long-lasting and freezer-friendly design. | Multipurpose Fridge Organisation Box Use it for meal prep, vegetable storage, freezer storage or kitchen organisation. Keeps your fridge neat, clean and clutter-free.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MoldBerry Silicone Chocolate Moulds Set of 2 | Heart &amp; Flower Shape Candy Molds for Chocolate, Jelly, Gummies | Flexible, Non-Stick, Reusable Baking Trays | Mini Silicone Molds for DIY Sweets</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41DzoKPZoeL._SY300_SX300_QL70_FMwebp_.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B04FssWFG</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Multipurpose Candy Molds Set – Includes 2 silicone moulds in adorable heart and flower designs, perfect for homemade chocolates, candies, jelly, mini soaps, ice cubes, or gummies. | Food-Grade &amp; Safe Silicone – Made from BPA-free, 100% food-grade silicone that is non-toxic, odorless, and heat-resistant up to 230°C. Safe for oven, microwave, freezer, and dishwasher. | Easy Release &amp; Non-Stick Surface – Flexible silicone ensures smooth release of chocolates without cracking or sticking—perfect for kids and beginners in baking and DIY candy-making. | Durable &amp; Reusable Moulds – These chocolate mould trays are long-lasting, eco-friendly, and washable, reducing single-use plastic and waste in your kitchen. | Ideal for Gifts &amp; Festive DIY – Make cute and creative chocolate treats for Valentine’s Day, birthdays, baby showers, wedding favors, or holiday gifting. Great fun for kids too!</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Kmils Oil Dispenser Bottle, Oil Spray Bottle for Cooking, Oil Sprayer for Air Fryer, Oil and Vinegar Pourer and sprayer bottle, Kitchen Oil Bottle | 500ml (Multicolor)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71RyWgU+rcL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0hyO1c4k</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>This olive oil dispenser has a built-in spout. You can switch between spray and pour functions at any time. | The nozzle of this oil spray bottle has been upgraded to achieve a uniform fan-shaped spray. The upgraded anti-drip design realizes no dripping or hanging on the wall when pouring oil. | This oil bottles for kitchen is made of thickened lead-free glass material, sturdy and durable. The clear bottle lets you know exactly how much oil is left. Olive oil spray bottle of lid and handle are made of food grade PP material, BPA free. | The spout of this oil sprayer for cooking air fryer has been widened, which is very convenient for pouring sunflower oil, vinegar, soy sauce, lemon and lime juice, sherry or marsala wine, etc. | This olive oil spray bottle has an ergonomic handle. The handle is comfortable to hold. The body of the pot is not easy to hang oil, and it is easy to clean. Dishwasher safe.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Lifelong Stainless Steel Cooking Utensils Set – 5 Piece Serving Spoon Set for Kitchen with Ladle, Skimmer, Spatula, Basting and Rice Spoon – Kitchen Utensil Set for Daily Use (LLCTKT05, Silver)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71B3Q7JoZ7L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B02EMl7jF</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Made from stainless steel for long lasting durability, resistant to rust and suitable for regular kitchen use. Built to withstand everyday wear and tear while maintaining its shine and strength over time | Includes ladle, skimmer, spatula, basting spoon, and rice spoon for a variety of cooking and serving needs. Each tool is thoughtfully shaped for optimal functionality during cooking and serving | Designed for daily cooking tasks like mixing, turning, serving, and more, Ideal for preparing all types of meals, from quick breakfasts to full course dinners | Crafted with smooth edges and balanced weight for easy and safe handling. Comfortable grip ensures better control and minimizes strain during prolonged use | Suitable for home cooks and beginners, an excellent addition to any kitchen setup, from starter kits to seasoned setups</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Xmart India Manual Push Chopper, 1000ML, 5 Stainless Steel Blades, Multicolor, Kitchen Essentials</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41qSSJTB2pL._SY300_SX300_QL70_FMwebp_.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B067F6OTk</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Multipurpose Hand Chopper for Effortless Prep : Chop, dice, mince, and crush a variety of ingredients including onions, garlic, tomatoes, fruits, nuts, and herbs in seconds with this versatile manual push chopper—perfect for daily kitchen use. | High-Quality 5 Stainless Steel Blades : Equipped with ultra-sharp, premium stainless steel blades placed at multiple levels to ensure fast and even chopping every time. Designed for maximum efficiency and durability. | Easy to Use, Clean &amp; Disassemble : Simply place ingredients in the bowl, close the lid, and push the handle for quick results. The blades and bowl are top-rack dishwasher safe for easy cleanup. | Unique Locking System for Safety &amp; Storage : Features a smart locking mechanism that secures the blade and handle when not in use—enhancing safety and saving storage space in your kitchen. | Food Grade Material with Non-Slip Base : Made from BPA-free, food-safe plastic with a non-skid base for stable and firm grip while chopping. Compact, durable, and ideal for every Indian kitchen.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Carrot Kitchen Knife Stainless Steel 2 Pieces Professional Knife Set with Color Printing and Non-Slip Handle (Multi Color Printed)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61HVB+lvk6L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B03b2QcGJ</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Stainless Steel: This 2-piece knife set for kitchen is made from high quality stainless steel, which provides good toughness and does not bend and break. The blade was polished and sharpened by hand which makes it extremely sharp, can help you quickly complete your cutting tasks in the kitchen. | Durable Print Food Grade Coating: Come with food grade print coating so that food cannot stick when cutting, also it can protect your knife blade from rust. Moreover, the colour of the printed coating does not fade over time ( with proper maintenance) ensure the long-lasting use of the product | Ergonomic Handle: The smooth and streamlined handle fits perfectly in the palm of your hand, easy to grip. All handles are made of PP material for a comfortable grasp and a long lasting grip. The grip and blade of the chef knife do not come off easily. Besides, it is a dishwasher safe knife set, which doesn't take much time to clean, saving your labor time! | All-in-one Economical Set: This kitchen kinfe set including one chef knife and one paring Knife. This essential multifunctional kitchen utensil set will quickly help you with all the tasks in the kitchen. | A Nice Gift for the Chef: This versatile knife set is not only for the kitchen, it can also be used for outdoor picnics, camping, hiking and other activities. Moreover, it makes a great kitchen gifts for your family and friends who love to cook and is suitable for numerous activities.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Home Improvement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Scotch-Brite Small wiper for Kitchen, Bathroom, Dinning tables, car windows wiping, instant dry surface, Superior TPE Blade, moulded handle</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61aGaJ-+gaL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B08gZDwiX</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Streak free single swipe clean for a instant dry surface | High quality TPE blade with durable handle | Ergonomic handle easy to hold and use | Lasts longer</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Health, Household &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cleevo Kitchen Cleaner Spray 1L Bottle Pack (2 Sachets makes 1 Litre)|Powder to Liquid | | Non-Toxic Degreaser for Gas Stove, Chimney &amp; Countertop | Surface Cleaner (Lilly)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71KORGe2RFL._SY450_PIbundle-5,TopRight,0,0_AA450SH20_.jpg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0ipHxkf1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Cleevo kitchen cleaning spray is ideal for oil &amp; grease stain remover tasks, providing powerful cleaning for kitchen tiles, gas stoves, chimneys, countertops, and ensuring hygienic, spotless surfaces. | Powerful kitchen cleaner liquid dissolves stubborn grease and grime fast, helping you maintain sparkling clean kitchen tiles, chimneys, and stovetops without harsh chemicals, ensuring safe daily use. | Convenient kitchen cleaner spray design offers precise coverage for targeted cleaning, reaching tricky corners and surfaces, making it perfect for deep cleaning and regular kitchen maintenance. | Gentle yet effective grease cleaner for kitchen surfaces, leaving no residue behind; enjoy a mild, fresh fragrance that eliminates cooking odors, creating a clean, refreshing kitchen environment.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Rechargeable Keychain Light | Multipurpose Home Kitchen Essentials Utility Products for Daily Use and Organization ORE-P039</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31ed9m3hX1L._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B065gV2eU</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Multipurpose Utility ? Suitable for home, kitchen, office, travel, personal care, and daily use. | Durable &amp; Reliable ? Made with quality materials for long-lasting performance. | Easy to Use ? Simple design ensures hassle-free operation for all users. | Compact &amp; Lightweight ? Easy to carry, store, and use anywhere. | Ideal for Daily Needs ? Perfect for cleaning, organization, repair, grooming, fitness, and household tasks.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Ceramic Bath Accessories Set of 3 (Luxe Black) – 400ml Soap Dispenser, Tumbler &amp; Soap Dish, Black with Gold Marble Design, Bathroom Countertop Organizer for washbasin</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51LF076gyTL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0b6UFNVW</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>COMPLETE 3-PIECE SET which includes 1 Soap Dispenser (400ml), 1 Tumbler (for toothbrush/paste), and 1 Soap Dish, perfectly coordinated for a neat and organized wash basin. | ELEGANT BLACK GOLD MARBLING makes it an Aesthetic design with a rich matte black tone and metallic marbling that adds instant sophistication to any space. | DURABLE CERAMIC BUILD is Crafted from high-quality ceramic for a sturdy, stable, and long-lasting finish. Scratch-resistant surface maintains its elegant look over time. | 400ML SOAP DISPENSER WITH PREMIUM PUMP reduces frequent refills. This Large-capacity dispenser comes with a smooth gold finish pump ensures easy, mess-free dispensing for liquid soap, handwash, lotion, or sanitizer. | PERFECT FOR GIFTING &amp; HOME UPGRADE this is an ideal bath accessories set for bathrooms, powder rooms, guest washrooms, or as a stylish housewarming gift.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Home Improvement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Scotch-Brite Sponge Wipes- Reusable, Kitchen and House Cleaning- Easy to use, Cleans any mess in a swipe, Absorbs water its own 10x weight, Multi- color, Biodegradable (pack of 3)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/712IgUo8fjL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B03yd3Slr</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Single swipe clean for a mess free kitchen | The cellulose based sponge cleans any mess in a single swipe | Absorbs water 10 times its own weight | Does not leave behind any water marks while swiping | Completely lint free and 100% scratch free cleaning</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Small PU Leather Jewelry Box01 | Multipurpose Home Kitchen Essentials Utility Products for Daily Use and Organization ORE-P069</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31BqRhe6PZL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0aLkwn1s</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Multipurpose Utility ? Suitable for home, kitchen, office, travel, personal care, and daily use. | Durable &amp; Reliable ? Made with quality materials for long-lasting performance. | Easy to Use ? Simple design ensures hassle-free operation for all users. | Compact &amp; Lightweight ? Easy to carry, store, and use anywhere. | Ideal for Daily Needs ? Perfect for cleaning, organization, repair, grooming, fitness, and household tasks.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Silicon Socks | Multipurpose Home Kitchen Essentials Utility Products for Daily Use and Organization ORE-P028</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41-ERHrZ5VL.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0hA7aGXu</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Casual Modern Women Socks | Multipurpose Home Kitchen Essentials Utility Products for Daily Use and Organization ORE-P098</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/3122YJpTxtL.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B02d4pq0V</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Keychain Storage Container Set of 3 White 1 | Home &amp; Kitchen Essentials ? Durable, Multipurpose &amp; Stylish Products</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31EmQzKxBnL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0fIC2KTs</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Premium Quality Materials ? Built with durable, safe, and long-lasting materials for daily household use. | Multi-Purpose Utility ? Ideal for cooking, cleaning, organizing, and enhancing your home &amp; kitchen efficiency. | Modern &amp; Practical Design ? Stylish look combined with user-friendly features to complement any home dcor. | Easy to Use &amp; Maintain ? Lightweight, convenient, and simple to clean, making everyday tasks hassle-free. | Perfect for Every Home ? Suitable for apartments, offices, and family kitchens, making them an essential addition.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Efficient Kitchen Stand with Knife Holder and Utensil Compartments Comfortable and Stylish Clothing with Modern Accessories|HV_-P362</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/31O2x4YlhQL.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B078AHzhd</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Health, Household &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Happi Planet Magic Eraser | Pack of 4 | No Scratch Multi-Surface Cleaning Sponge | Removes 100+ Tough Stains | Just Add Water | Walls, Kitchen, Bathroom, Shoes &amp; Switch Boards</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/51CEc354bZL._SX425_.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0hgLwaZr</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>INSTANTLY REMOVES STUBBORN STAINS: Easily removes crayon marks, pencil scribbles, grease, soap scum, shoe marks, limescale and more — no harsh chemicals required. | REQUIRES ONLY WATER: Just soak, squeeze and wipe. No detergents or sprays needed. Safe and simple everyday cleaning solution. | NO SCRATCH FORMULA: Designed to clean effectively without damaging surfaces. Gentle yet powerful micro-abrasive foam technology. | MULTI-SURFACE CLEANING: Perfect for walls, bathroom tiles, kitchen surfaces, plastic chairs, switch boards, shoes, doors and more. | EASY TO USE: Soak in water, Press out excess water and Gently erase stains. | VALUE PACK OF 4: Long-lasting erasers designed for multiple uses. Ideal for home, office and car cleaning needs.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Shoes and Handbags</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Canvas Tote Bag for Women with Zipper Closure | Eco-Friendly Reusable Shoulder Bag | Sturdy Handles for Shopping, Office, College &amp; Casual Use</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71yOTT5H8zL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0FYDCH8YX?th=1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Shoes and Handbags</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ZOUK Jute Handcrafted Vegan Leather Women's Shoulder Luna Handbags</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/81fJbLaIKLL._SY695_.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CL9P14JH?th=1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pigeon Mio Nonstick Aluminum Cookware Gift Set, Includes Flat Tawa, Fry Pan, Kadai with Glass Lid, Kitchen Tool Set, Black, 8 Pieces</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61w2eRTCulL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0C24BK3Z2?th=1</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Material: Aluminium Blend | Color: Black | Style: Modern | Included Components: Cookware Set | Special Features: High Quality</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pigeon Favourite 7 Piece Gift Set Non-Stick Coated Comes with Fry Pan, Kadhai, Lid, Sauce Pan, Spatula, Tadka Pan and a Tawa - Gas Stove Compatible (Red)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61aZ1CUskVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B073316W2J?th=1</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Heat Resistant Bakelite Handles For Easy Grip | 7 Piece Forged Gift Set | Pure Coat Technology | 5 Layer Teflon Coating from Dupont USA | Chemical Pfoa Free And Scratch Resistant</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Kitchen Pride Non-Stick Cookware Set of 5 | Includes Nonstick Tawa, Frying Pan, Kadhai with Lid, Nylon Laddle &amp; Spatula | Non-Induction Base | Peach Color</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71rCioa7fGL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CSYYQ82J?th=1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | HEAT-RESISTANT HANDLE: Our cooking utensils comes with bakelite handle offers a secure, comfortable grip and stays cool for safe, easy cooking. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC : Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET: Color: Peach; Material: Aluminium; Package Content: 5 - Pieces Kitchen Pride Plus Non Induction Set . 1 Piece Non Stick Tawa 25cm, 1 Piece Fry Pan 24cm/1.6 litres, 1 Piece Kadhai with Glass Lid 24cm/2.5 litres, Nylon Laddle &amp; Spatula</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Induction Cookware &amp; Gas Stove Friendly Kitchen Jewel Set | 5 Pc Non-Stick Cookware Set | Kadhai with Lid, Fry Pan, Tawa, Laddle &amp; Spatula | Durable 5-Layer Non Stick Coating | Peach</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/711stZJUuFL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B5XRDRFH?th=1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | INDUCTION COOKWARE &amp; GAS STOVE FRIENDLY: Features a versatile base cooking utensils that ensures efficient, hassle-free cooking on both induction and gas cooktops. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC: Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET : Peach Colour ; Material: Aluminium; Package Content: 3 - Pieces Kitchen Jewel Set (1 - Piece Fry Pan, 24 cm; 1 - Piece Kadhai with Glass Lid, 24 cm; 1 - Piece Tawa, 25 cm 1 - Piece Nylon Laddle; 1 - Piece Nylon Spatula</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|25 Cm Tawa,22 Cm Fry Pan,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/719hJsjR3ZL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYBQB8T</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 25 cm Tawa, 22 cm Fry Pan, 1 Glass Lid</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pigeon Aluminium Nonstick Duo Pack Flat Tawa 250 and Fry Pan 200 Gift Set (Red)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/510yXR4GoNL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07KYPZHJ9</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>5 Layer Durable Nonstick Coating. Broiler :Safe | Made with High End Italian Technology | Oil Free Cooking | Ergonomic Bakelite Handle | Free from Peel-Off</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Prestige Non-Stick 3 Pc Cookware Set with Stainless Steel Lid | Omega Select Plus | Omni Tawa 25cm | Fry Pan 25cm | Kadai 25cm | PFOA Free | Metal Spoon Friendly | Sturdy Handles | 1Y Warranty | ISI</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51sTQ6mcf9L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00EICKVUA?th=1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗦𝗘𝗧: Includes Omni Tawa (25 cm), Fry Pan (25 cm), and Kadai (25 cm) with 1 Stainless Steel Lid (25 cm) — a complete everyday set for making dosas, stir-fries, curries, and sautéing. | 𝗦𝗨𝗣𝗘𝗥𝗜𝗢𝗥 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: High-quality aluminium cookware set with a non-stick coating that ensures residue-free cooking with less oil and easy food release. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free coating ensures healthy, toxin-free cooking every day. | 𝗦𝗖𝗥𝗔𝗧𝗖𝗛 &amp; 𝗔𝗕𝗥𝗔𝗦𝗜𝗢𝗡 𝗥𝗘𝗦𝗜𝗦𝗧𝗔𝗡𝗧 𝗧𝗘𝗖𝗛𝗡𝗢𝗟𝗢𝗚𝗬: Advanced coating resists scratches and corrosion on the non-stick surface, ensuring long-lasting durability and smooth performance. | 𝗠𝗘𝗧𝗔𝗟 𝗦𝗣𝗢𝗢𝗡 𝗙𝗥𝗜𝗘𝗡𝗗𝗟𝗬: Tough 3-layer coating withstands regular metal spoon use, keeping the surface safe and functional for years. | 𝗦𝗧𝗔𝗜𝗡𝗟𝗘𝗦𝗦 𝗦𝗧𝗘𝗘𝗟 𝗟𝗜𝗗: Flat-base Kadai comes with a durable stainless steel lid for safe cooking and easy serving. | 𝗚𝗔𝗦 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Suitable for gas stoves only. Ergonomic, heat-resistant handles provide a secure and comfortable grip. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟭-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and performance, backed by a 1-year Prestige warranty covering manufacturing defects.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Non-Stick 3 Pc Cookware Set with Glass Lid | 5-Layer Coating | Gas &amp; Induction Compatible | Omni Tawa 25cm | Fry Pan 24cm | Kadai 24cm | Crimson Red |2Y Warranty |ISI Certified</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51OUmYcUalL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DXRFR6</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗖𝗢𝗠𝗕𝗢 𝗦𝗘𝗧: Includes Omni Tawa 25 cm, Fry Pan 24 cm, Kadai 24 cm, and a 24 cm Glass Lid—a complete everyday kit for dosas, stir-fries, curries, and sautéing. | 𝗜𝗡𝗗𝗜𝗔’𝗦 𝗙𝗜𝗥𝗦𝗧 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗪𝗜𝗧𝗛 𝟱-𝗟𝗔𝗬𝗘𝗥 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Designed using advanced German technology, the 5-layer non-stick coating ensures superior durability, long life, and metal-spoon friendliness. | 𝗗𝗨𝗥𝗔𝗕𝗟𝗘 𝗚𝗥𝗔𝗡𝗜𝗧𝗘-𝗙𝗜𝗡𝗜𝗦𝗛 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Stylish granite finish offers a premium look while providing a tough, scratch- and abrasion-resistant surface for lasting performance. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free non-stick coating ensures healthy, toxin-free meals every time. | 𝗧𝗪𝗢-𝗟𝗔𝗬𝗘𝗥 𝗠𝗘𝗧𝗔𝗟𝗟𝗜𝗖 𝗙𝗜𝗡𝗜𝗦𝗛 𝗘𝗫𝗧𝗘𝗥𝗜𝗢𝗥: Dual-layer metallic coating on the exterior maintains its elegant look even after extended use and repeated washing. | 𝗗𝗜𝗦𝗛𝗪𝗔𝗦𝗛𝗘𝗥 𝗦𝗔𝗙𝗘: Easy to clean and maintain — compatible with dishwashers for convenient, everyday use. | 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 𝗪𝗜𝗧𝗛 𝗚𝗔𝗦 &amp; 𝗜𝗡𝗗𝗨𝗖𝗧𝗜𝗢𝗡 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Works efficiently on both gas and induction cooktops. Ergonomically designed stay-cool handles ensure safe and comfortable handling. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟮-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and quality, backed by a 2-year Prestige warranty for assured reliability and peace of mind.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Milton Pro Cook Kitchen Pride Plus Granito I Set of 7 Non Stick Cookware | Non Induction I Cooking Pan, Kadhai with Lid, Tawa, Nylon Laddle &amp; Spatula I Peach Metallic</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/713YqQo-9zL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DXQ1V29L?th=1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>50 YEARS OF INDIAN INNOVATION: Milton, India's trusted household name for unmatched quality and reliability. | 5 LAYER NON-STICK COATING: Advanced coating technology delivers fast, even cooking while preventing food from sticking and ensuring long-lasting performance. | HEAT-RESISTANT HANDLE: Our cooking utensils comes with bakelite handle offers a secure, comfortable grip and stays cool for safe, easy cooking. | ENHANCE FLAVORS WITH LESS OIL: Experience healthier cooking designed for minimal oil use and easy cleanup, so every dish is delicious and effortless. | PFOA FREE &amp; NON TOXIC : Made from superior quality Aluminium PFOA FREE material, making it is safe for daily use with no harmful chemicals, making cooking healthier and completely worry-free. | BACKED BY 1 YEAR WARRANTY: Enjoy peace of mind with reliable support and assured quality for confident daily use. | WHAT YOU GET: Color: Peach Metallic; Material: Aluminium; Non Induction 7pc Set (Fry pan 24cm/1.6 LTR; Kadhai 24cm/2.5 LTR with Glass Lid; Tawa 25cm; 2 Nylon Laddle &amp; Spatula)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Wonderchef Valencia Non-Stick 4 Pc Cookware Set for Kitchen, Fry Pan 24cm, Kadhai with Glass Lid 24cm, Dosa Tawa 28cm, Non-Toxic PFOA Free, Gas Stove &amp; Induction Friendly, 2-Yr Warranty, Purple</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71Qm7r1QfPL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09QPS9BDV?th=1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>VERSATILE 4-PIECE SET - Kadhai with Lid 24 cm, Fry Pan 24 cm, Dosa Tawa 28 cm let you cook various dishes like cutlets, curries, dosas, omelets, and more with just one cookware set. | HEALTHY COOKING MADE EASY: MetaTuff 5-layer non-stick coating ensures minimal oil use, excellent abrasion resistance and is 100% free from PFOA, lead, cadmium, nickel, and arsenic and approved by USFDA and European Food Safety Authority (EFSA). | VERSATILE: Cook delicious cutlets, stir-fry veggies, curries, dosas, uttapams, sandwiches, omelets, and parathas with the fry pan, kadhai, and tawa. Complete your cookware needs with Valencia set! | ENERGY-EFFICIENT: Pure grade virgin aluminium offers 9-times better heat conduction, cooking your meals faster while saving energy and time. | COMPATIBLE WITH ALL COOKING SURFACES - Use on gas cooktopS, hot plates, infrared cooktops, and ceramic cooktops for maximum flexibility in your kitchen. | COMFORTABLE &amp; STYLISH - Cool touch Bakelite handles provide a firm grip and utmost convenience. Enjoy cooking with comfort and ease. | CONVENIENT: Easy to clean and dishwasher safe. Lightweight for daily use. | IDEAL FOR GIFTING - Loaded with features and beautiful looks, the Valencia cookware set is an ideal choice for gifting. Surprise your loved ones with a perfect addition to their kitchen.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Prestige Omega Granite Non-Stick 3 Pc Cookware Set with Glass Lid | 5-Layer Coating | Gas &amp; Induction Compatible | Omni Tawa 25cm | Fry Pan 24cm | Kadai 24cm | Moss Green | 2Y Warranty |ISI Certified</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61Z62Y9QubL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DY7TPK</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>𝗩𝗘𝗥𝗦𝗔𝗧𝗜𝗟𝗘 𝟯-𝗣𝗜𝗘𝗖𝗘 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗖𝗢𝗠𝗕𝗢 𝗦𝗘𝗧: Includes Omni Tawa 25 cm, Fry Pan 24 cm, Kadai 24 cm, and a 24 cm Glass Lid—a complete everyday kit for dosas, stir-fries, curries, and sautéing. | 𝗜𝗡𝗗𝗜𝗔’𝗦 𝗙𝗜𝗥𝗦𝗧 𝗡𝗢𝗡-𝗦𝗧𝗜𝗖𝗞 𝗖𝗢𝗢𝗞𝗪𝗔𝗥𝗘 𝗪𝗜𝗧𝗛 𝟱-𝗟𝗔𝗬𝗘𝗥 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Designed using advanced German technology, the 5-layer non-stick coating ensures superior durability, long life, and metal-spoon | 𝗗𝗨𝗥𝗔𝗕𝗟𝗘 𝗚𝗥𝗔𝗡𝗜𝗧𝗘-𝗙𝗜𝗡𝗜𝗦𝗛 𝗖𝗢𝗔𝗧𝗜𝗡𝗚: Stylish granite finish offers a premium look while providing a tough, scratch- and abrasion-resistant surface for lasting performance. | 𝗣𝗙𝗢𝗔-𝗙𝗥𝗘𝗘 &amp; 𝗦𝗔𝗙𝗘 𝗖𝗢𝗢𝗞𝗜𝗡𝗚: 100% PFOA-free non-stick coating ensures healthy, toxin-free meals every time. | 𝗧𝗪𝗢-𝗟𝗔𝗬𝗘𝗥 𝗠𝗘𝗧𝗔𝗟𝗟𝗜𝗖 𝗙𝗜𝗡𝗜𝗦𝗛 𝗘𝗫𝗧𝗘𝗥𝗜𝗢𝗥: Dual-layer metallic coating on the exterior maintains its elegant look even after extended use and repeated washing. | 𝗗𝗜𝗦𝗛𝗪𝗔𝗦𝗛𝗘𝗥 𝗦𝗔𝗙𝗘: Easy to clean and maintain — compatible with dishwashers for convenient, everyday use. | 𝗖𝗢𝗠𝗣𝗔𝗧𝗜𝗕𝗟𝗘 𝗪𝗜𝗧𝗛 𝗚𝗔𝗦 &amp; 𝗜𝗡𝗗𝗨𝗖𝗧𝗜𝗢𝗡 | 𝗦𝗧𝗔𝗬-𝗖𝗢𝗢𝗟 𝗕𝗔𝗞𝗘𝗟𝗜𝗧𝗘 𝗛𝗔𝗡𝗗𝗟𝗘𝗦: Works efficiently on both gas and induction cooktops. Ergonomically designed stay-cool handles ensure safe and comfortable handling. | 𝗜𝗦𝗜 𝗖𝗘𝗥𝗧𝗜𝗙𝗜𝗘𝗗 &amp; 𝟮-𝗬𝗘𝗔𝗥 𝗪𝗔𝗥𝗥𝗔𝗡𝗧𝗬: ISI-certified for safety and quality, backed by a 2-year Prestige warranty for assured reliability and peace of mind.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo 6 Piece Non-Stick Cookware Set | Granite Finish | Induction Base | PFOA Free | HTR Exterior Coating | 25cm Tawa, 22 cm Kadai, 22cm Fry Pan, 1 Glass Lid &amp; 2 Nylon Spatulas | Grey</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61etK-QYt+L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYCF584?th=1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Impex 6 Pcs Nonstick Granite Cookware Set | 3mm Thick Induction Base | Kadai with Glass Lid, Frypan, Tawa, Tadka Pan &amp; Milk Pan | Gas &amp; Induction Compatible Cookware Set | PFOA Free | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/612471TQz1L._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CX4KLN26</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>🍳 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟔-𝐏𝐈𝐄𝐂𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘𝐃𝐀𝐘 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Includes 240mm Kadai with Glass Lid, 240mm Frypan, 240mm Tawa, 160mm Milk Pan &amp; 90mm Tadka Pan – handles frying, sautéing, tempering, dosa-making, curries &amp; warming milk in one set. | 💎 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊 𝐁𝐎𝐃𝐘 𝐖𝐈𝐓𝐇 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Advanced granite nonstick coating ensures superior heat retention, even cooking &amp; long-lasting nonstick performance – less oil needed for healthier, tastier everyday meals. | 🔥 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Induction bottom base works seamlessly across gas stoves, induction cooktops &amp; electric hobs, giving you complete flexibility to cook anywhere in a modern or traditional Indian kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄, 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂 &amp; 𝐅𝐎𝐎𝐃 𝐒𝐀𝐅𝐄: Premium nonstick granite coating is completely PFOA free, ensuring a safer cooking surface with no harmful chemical leaching into your family's food, meal after meal. | ✋ 𝐄𝐑𝐆𝐎𝐍𝐎𝐌𝐈𝐂 𝐂𝐇𝐑𝐎𝐌𝐄 𝐏𝐋𝐀𝐓𝐄𝐃 𝐇𝐀𝐍𝐃𝐋𝐄𝐒: Sturdy chrome-plated mounted handles with detachable knobs plus stainless steel wire handles give a secure, cool-touch grip, easy maneuverability &amp; compact space-saving storage. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖-𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: Super granite nonstick surface with even heat distribution lets you cook flavourful, nutritious meals using minimal oil, cutting down fat while keeping every dish deliciously moist and evenly cooked. | 🧽 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓 𝐒𝐔𝐑𝐅𝐀𝐂𝐄: The tough nonstick granite coating resists scratching from daily use and wipes clean effortlessly, saving you time and effort on kitchen cleanup after every meal. | 🍽️ 𝐀𝐋𝐋-𝐈𝐍-𝐎𝐍𝐄 𝐈𝐍𝐃𝐈𝐀𝐍 &amp; 𝐌𝐔𝐋𝐓𝐈-𝐂𝐔𝐈𝐒𝐈𝐍𝐄 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄: Kadai for curries &amp; deep frying, Tawa for dosa/roti, Tadka Pan for tempering spices, Frypan for sauteing &amp; Milk Pan for boiling – one set for your entire kitchen. | 🎁 𝐏𝐄𝐑𝐅𝐄𝐂𝐓 𝐆𝐈𝐅𝐓 𝐒𝐄𝐓 𝐅𝐎𝐑 𝐄𝐕𝐄𝐑𝐘 𝐎𝐂𝐂𝐀𝐒𝐈𝐎𝐍: An elegant, practical cookware gift set ideal for weddings, housewarmings, festivals &amp; new home kitchens – a thoughtful present that upgrades everyday cooking instantly. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐃𝐔𝐑𝐀𝐁𝐋𝐄 𝐁𝐔𝐈𝐋𝐃: Backed by Impex's 1-year manufacturer warranty, this rust-resistant, long-lasting cookware set is engineered for reliable daily performance in Indian households for years.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 6 Piece Non-Stick Cookware Set with Detachable Handle| Granite Finish | Induction Base | Pfoa Free | HTR Exterior Coating | Black</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61WoqAJEnIL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZW8NVFN</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 6 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, Laddle &amp; Spatula | Durable 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/812-MTsU4AL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41BFBBB?th=1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Elegant white marble finish enhances kitchen aesthetics | Induction base suitable for gas stove and induction cooktops | Superior nonstick coating prevents food sticking | Saves cooking oil for healthier meals | Strong and sturdy construction for regular use</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Prestige Omega Deluxe Granite Aluminium 3 Pcs Set- Tawa, Fry Pan &amp; Kadai with 1 Glass Lid|Non-Stick|Spatter-Coated Surface|Induction &amp; Gas Compatible|Black</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/617m8cRiYkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01H932RC4</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Made using German technology and it lasts three times longer than ordinary non-stick cookware. | Special spatter-coated surface looks new for longer and is also metal-spoon friendly | Can be used on both gas and induction cook-tops. | Durable Granite-finish Coating Dishwasher Safe Superior Non-stick Surface Cook &amp; Serve | Warranty : 2 Years Manufacturer Warranty</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DOZY 5-Piece Non-Stick Cookware Combo Set with Kadhai, Tawa &amp; Tadka Pan Induction Bottom Non-Stick Coated Cookware Set (Iron-Rich Nonstick Cookware Combo)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61V9hrdORHL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H1WBB126?th=1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>COMPLETE 5-PIECE SET: Includes a Kadhai, Tawa, Tadka Pan, and additional cookware pieces to cover all your everyday Indian cooking needs. | PREMIUM NON-STICK COATING: Superior non-stick surface ensures food slides off effortlessly, making cooking and cleaning quick and hassle-free. | INDUCTION COMPATIBLE: Specially designed with an induction-friendly bottom, making this cookware set compatible with all types of cooktops. | ERGONOMIC HANDLES: Fitted with sturdy, heat-resistant handles for a secure and comfortable grip while cooking, ensuring safe handling at all times. | DURABLE CONSTRUCTION: Handcrafted from high-quality materials with even heat distribution for consistent, perfectly cooked results every time.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Hawkins Futura 5 Pieces Cookware Set 4 - Non Stick Kadhai, Two Frying Pans, Saucepan, Saute Pan and Two Glass Lids, Black (NSET4)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61T0Fe6un2S._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B00EVR0CRY?th=1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PFOA Free Non-stick coating locked into tough Hard Anodised Aluminium - lasts longer | The cookware set consists two Frying Pans, Deep-Fry Pan (Stir-Fry Pan), Saucepan with glass lid and Curry Pan (Sauté Pan) with glass lid to cater to most of your cooking needs | There is attractive saving on the purchase of the Set when compared with buying individual items separately | Each item included in the Set is accompanied by its own Instruction Manual / Cookbook and its own Guarantee Card | Suitable for use on domestic gas, electric, ceramic and halogen stoves</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Prestige Omega Deluxe Non-Stick Cookware 3 Pc Set |PFOA Free 5-Layer Coating | Omni Tawa 25 cm | Fry Pan 24 cm | Kadai with Glass Lid 24 cm | Brown | Dishwasher Safe</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/61eTcL4tdkL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0B4DY7TD6</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>India's First Non-Stick Cookware with 5-Layers Coating | Durable Granite-finish Coating | Two-layer Metallic Finish Exterior | Superior Non-stick Surface | Dishwasher Safe | Stay-cool Bakelite Handles | Gas Stove and Induction Compatible | PFOA Free</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Crystal Aluminum 11 Pcs Non Stick Cookware Set with Induction Bottom | Tawa, Fry Pan, Kadhai with Lid, 4 Serving Spoons, 3 Containers | 4 Layer Non Stick Coating | PFOA Free | White</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/71VFfXMdmeL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0H41FL5NG?th=1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Complete cookware set for versatile cooking requirements | Induction and gas stove compatible base | Elegant white marble nonstick interior and exterior | Even heat distribution for faster cooking | Heat resistant handles for safe and easy use</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Posted</t>
         </is>

--- a/data/posted_pins.xlsx
+++ b/data/posted_pins.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4612,6 +4612,134 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Impex Migo Nonstick Cookware Set 3 Pcs | Induction Bottom | 5 Layer Super Granite Coating | 3mm Thick Aluminium | PFOA Free | Gas &amp; Induction Compatible | Detachable Chrome Handle | 1 Yr Warranty</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/713olRvDhHL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CW3G6ZQC</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>🍳 𝐀𝐃𝐕𝐀𝐍𝐂𝐄𝐃 𝟓-𝐋𝐀𝐘𝐄𝐑 𝐒𝐔𝐏𝐄𝐑 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐂𝐎𝐀𝐓𝐈𝐍𝐆: Premium non-stick surface is 10X tougher than ordinary coatings, delivering smooth food release, effortless everyday cooking and easy cleanup for busy Indian kitchens. | ⚡ 𝐆𝐀𝐒 &amp; 𝐈𝐍𝐃𝐔𝐂𝐓𝐈𝐎𝐍 𝐂𝐎𝐌𝐏𝐀𝐓𝐈𝐁𝐋𝐄: Versatile induction bottom cookware works seamlessly across gas stoves, induction cooktops and other cooking surfaces, making it a flexible pick for modern and traditional kitchens alike. | 🥗 𝐇𝐄𝐀𝐋𝐓𝐇𝐘 𝐋𝐎𝐖 𝐎𝐈𝐋 𝐂𝐎𝐎𝐊𝐈𝐍𝐆: PFOA-free, non-toxic aluminium construction lets you cook nutritious, healthier meals with minimal oil, while keeping harmful chemicals away from your everyday family food and health. | 🔥 𝐎𝐏𝐓𝐈𝐌𝐀𝐋 𝟑𝐌𝐌 𝐓𝐇𝐈𝐂𝐊𝐍𝐄𝐒𝐒: Sturdy 3mm thick aluminium body ensures even heat distribution, faster heating and consistent cooking results, preventing hot spots so every dish cooks evenly and thoroughly every time. | ✋ 𝐃𝐄𝐓𝐀𝐂𝐇𝐀𝐁𝐋𝐄 𝐂𝐇𝐑𝐎𝐌𝐄 𝐇𝐀𝐍𝐃𝐋𝐄: Chrome-plated, sturdy detachable handle and knob provide a secure, comfortable grip while cooking, and allow for compact, space-saving storage in small, modern Indian kitchens. | 🧼 𝐄𝐀𝐒𝐘 𝐓𝐎 𝐂𝐋𝐄𝐀𝐍 &amp; 𝐒𝐂𝐑𝐀𝐓𝐂𝐇 𝐑𝐄𝐒𝐈𝐒𝐓𝐀𝐍𝐓: Granite-finish non-stick surface is scratch resistant and simple to wipe clean, saving valuable time on daily kitchen chores while keeping the shine looking brand new. | 🍲 𝐂𝐎𝐌𝐏𝐋𝐄𝐓𝐄 𝟑 𝐏𝐂𝐒 𝐂𝐎𝐎𝐊𝐖𝐀𝐑𝐄 𝐒𝐄𝐓: Ideal for frying, sauteing, tadka, curries and everyday Indian cooking, this practical cookware set gives you the essential pans needed for a fully equipped modern kitchen. | 🛡️ 𝐏𝐅𝐎𝐀 𝐅𝐑𝐄𝐄 &amp; 𝐍𝐎𝐍-𝐓𝐎𝐗𝐈𝐂: Health-conscious, food-grade aluminium construction is completely free from PFOA and harmful chemicals, ensuring safe, worry-free cooking for you and your entire family, every day. | 💎 𝐌𝐈𝐑𝐑𝐎𝐑-𝐋𝐈𝐊𝐄 𝐆𝐑𝐀𝐍𝐈𝐓𝐄 𝐅𝐈𝐍𝐈𝐒𝐇: Elegant granite finish gives your cookware a premium, modern look that enhances your kitchen decor while offering long-lasting, durable non-stick performance you can trust daily. | ✅ 𝟏 𝐘𝐄𝐀𝐑 𝐖𝐀𝐑𝐑𝐀𝐍𝐓𝐘 &amp; 𝐓𝐑𝐔𝐒𝐓𝐄𝐃 𝐐𝐔𝐀𝐋𝐈𝐓𝐘: Backed by a 1 year manufacturer warranty, this Impex nonstick cookware set is reliable, durable and a perfect gift choice for new homes, weddings and housewarmings.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Cello Prima 3 pcs Non-Stick Aluminium Cookware Set, Cherry Red (28 cm Dosa Tawa, 22 cm Kadai with Glass Lid, 22 cm Fry Pan) | Induction Base, PFOA-Free, Sturdy Handles, Ideal for Gifting</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/61YACQ7VkVL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07H94YY16?th=1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Upgrade your everyday cooking with the Cello Prima Non-Stick Aluminium Cookware Set, featuring a stylish and modern finish that enhances the look of your kitchen while providing a practical and reliable solution for preparing a wide variety of meals for your family. | This versatile cookware set includes a 22 cm Kadhai with a durable glass lid, a 22 cm Fry Pan, and a spacious 28 cm Dosa Tawa, making it perfect for cooking curries, stir-fries, sautéed vegetables, dosas, pancakes, omelets, and many other delicious recipes with ease. | Crafted from high quality aluminium, each cookware piece delivers quick and even heat distribution to ensure consistent cooking results, reduce cooking time, and improve energy efficiency, allowing you to prepare meals more effectively every day. | The premium non-stick coating promotes healthier cooking by requiring less oil while preventing food from sticking to the surface, making cooking smoother and cleanup faster, while the dishwasher-safe construction adds extra convenience for busy households. | Designed with a sturdy induction-compatible base that works efficiently on both gas stoves and induction cooktops, this durable cookware set combines functionality, convenience, and long-lasting performance, making it an ideal choice for modern kitchens and everyday cooking needs.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Amazon Brand - Solimo Aluminium 3 Piece Non-Stick Cookware Set|Granite Finish|Induction Base|Pfoa Free|High Temperature Resistant Exterior Coating|22 Cm Fry Pan,22 Cm Kadai,1 Glass Lid|Grey</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71NSco75mOL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZYDWLMV</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>HEAT CONDUCTIVITY: Made with pressed aluminium, the products in this set provide high conductivity which enables quick heat distribution and even cooking | PFOA-FREE: Being PFOA-free, the cookware is safe for daily use | NON-STICK: The non-stick feature makes it super convenient to use as food doesn't stick to the cookware | PHENOLIC HANDLES: This product has phenolic handles which remain cool to the touch during cooking | DISHWASHER-SAFE: The product is dishwasher-safe and hence, easy to clean and maintain | PACKAGE CONTENTS: 22 cm Fry Pan, 22 cm Kadai, 1 Glass Lid</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Kitchen &amp; Dining</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Judge by Prestige ACE Aluminium Non-Stick cookware BYK Set-Tawa 25cm-1U, Fry Pan 20cm-1U, Kadai 20cm-1U with Lid-1U + 3U Nylon Tools|Black</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/71XddeECOFL._SX679_.jpg</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DG8N3MTV</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Durable Body | Low Oil Cooking | Elegant Design | Cool Touch Handle</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
